--- a/docs/v2.0.0/ValueSet-VRM-CauseOfDeathCodingUpdateHeaderURI-vs.xlsx
+++ b/docs/v2.0.0/ValueSet-VRM-CauseOfDeathCodingUpdateHeaderURI-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:39:59-04:00</t>
+    <t>2026-10-16T16:24:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
